--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/42.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/42.xlsx
@@ -426,13 +426,13 @@
         <v>-9.199445136687972</v>
       </c>
       <c r="E2">
-        <v>-17.80490674042366</v>
+        <v>-26.88282159041989</v>
       </c>
       <c r="F2">
-        <v>-5.217637907260753</v>
+        <v>-5.324303464249635</v>
       </c>
       <c r="G2">
-        <v>-9.094188926685698</v>
+        <v>-16.31478835220746</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.723364642611037</v>
       </c>
       <c r="E3">
-        <v>-19.06740906597009</v>
+        <v>-26.64529407176956</v>
       </c>
       <c r="F3">
-        <v>-5.791235116757452</v>
+        <v>-5.400359188970269</v>
       </c>
       <c r="G3">
-        <v>-9.707023874733423</v>
+        <v>-15.63444310425015</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.135535750077709</v>
       </c>
       <c r="E4">
-        <v>-17.8035119704293</v>
+        <v>-27.29080087071893</v>
       </c>
       <c r="F4">
-        <v>-5.349925696385626</v>
+        <v>-5.386270316183455</v>
       </c>
       <c r="G4">
-        <v>-9.023465742330249</v>
+        <v>-15.34576022268016</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.483416032838016</v>
       </c>
       <c r="E5">
-        <v>-19.29693024257486</v>
+        <v>-28.04463782487978</v>
       </c>
       <c r="F5">
-        <v>-5.785175609205973</v>
+        <v>-5.468413712947262</v>
       </c>
       <c r="G5">
-        <v>-7.891219441353031</v>
+        <v>-15.16333095546585</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.773973907426975</v>
       </c>
       <c r="E6">
-        <v>-19.41775445757351</v>
+        <v>-27.70841221523228</v>
       </c>
       <c r="F6">
-        <v>-5.209442868544858</v>
+        <v>-5.17663123571997</v>
       </c>
       <c r="G6">
-        <v>-7.868121765125536</v>
+        <v>-15.21947946308466</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.0355478596942</v>
       </c>
       <c r="E7">
-        <v>-19.27668343528656</v>
+        <v>-28.67828907887706</v>
       </c>
       <c r="F7">
-        <v>-4.989333224109988</v>
+        <v>-5.312307875889696</v>
       </c>
       <c r="G7">
-        <v>-8.410932053926597</v>
+        <v>-15.10651040710257</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.277925672093577</v>
       </c>
       <c r="E8">
-        <v>-19.86151321100715</v>
+        <v>-28.83662264408125</v>
       </c>
       <c r="F8">
-        <v>-5.226324167846509</v>
+        <v>-5.336027348101457</v>
       </c>
       <c r="G8">
-        <v>-9.01041888235998</v>
+        <v>-15.03595275002409</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.511592317819036</v>
       </c>
       <c r="E9">
-        <v>-20.30676183238932</v>
+        <v>-29.14381167839157</v>
       </c>
       <c r="F9">
-        <v>-5.48993966827641</v>
+        <v>-5.39687093383708</v>
       </c>
       <c r="G9">
-        <v>-7.851896781437568</v>
+        <v>-14.40120364577916</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-3.750631229274228</v>
       </c>
       <c r="E10">
-        <v>-20.7686118394836</v>
+        <v>-29.70572737563334</v>
       </c>
       <c r="F10">
-        <v>-5.104164826955667</v>
+        <v>-5.271734440500575</v>
       </c>
       <c r="G10">
-        <v>-6.593733880874171</v>
+        <v>-13.96498133643324</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-3.011456790825436</v>
       </c>
       <c r="E11">
-        <v>-21.68176956618231</v>
+        <v>-30.07583729204324</v>
       </c>
       <c r="F11">
-        <v>-5.272342462174231</v>
+        <v>-5.315629629174921</v>
       </c>
       <c r="G11">
-        <v>-7.668687880748761</v>
+        <v>-13.3731782841965</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-2.309445167482325</v>
       </c>
       <c r="E12">
-        <v>-22.97679539205184</v>
+        <v>-30.97593489970383</v>
       </c>
       <c r="F12">
-        <v>-4.094140594559243</v>
+        <v>-5.268699302336718</v>
       </c>
       <c r="G12">
-        <v>-6.160287463962933</v>
+        <v>-13.45967621804658</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-1.662122507621605</v>
       </c>
       <c r="E13">
-        <v>-23.9168477258821</v>
+        <v>-31.27992456712773</v>
       </c>
       <c r="F13">
-        <v>-4.933985027724536</v>
+        <v>-5.341086187830353</v>
       </c>
       <c r="G13">
-        <v>-6.804109118258237</v>
+        <v>-13.24309039723084</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-1.101385909664898</v>
       </c>
       <c r="E14">
-        <v>-22.24976700401639</v>
+        <v>-31.73948316637413</v>
       </c>
       <c r="F14">
-        <v>-4.980820092311417</v>
+        <v>-4.998329294104391</v>
       </c>
       <c r="G14">
-        <v>-6.406380177170196</v>
+        <v>-12.59182332601772</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-0.649526842993902</v>
       </c>
       <c r="E15">
-        <v>-23.77479402473549</v>
+        <v>-32.3037581985739</v>
       </c>
       <c r="F15">
-        <v>-5.008113141498855</v>
+        <v>-5.018106565846228</v>
       </c>
       <c r="G15">
-        <v>-5.063119703519834</v>
+        <v>-12.95411287710786</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.3217639629971545</v>
       </c>
       <c r="E16">
-        <v>-24.80096887724363</v>
+        <v>-32.48150080337496</v>
       </c>
       <c r="F16">
-        <v>-4.476847163020017</v>
+        <v>-5.138426931102857</v>
       </c>
       <c r="G16">
-        <v>-5.851714824793006</v>
+        <v>-12.15609594322992</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.1253023610229032</v>
       </c>
       <c r="E17">
-        <v>-25.49029319069122</v>
+        <v>-32.93956274196184</v>
       </c>
       <c r="F17">
-        <v>-4.666433125396532</v>
+        <v>-4.646563904872983</v>
       </c>
       <c r="G17">
-        <v>-4.645527489196167</v>
+        <v>-11.64913224152809</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.05482140492461566</v>
       </c>
       <c r="E18">
-        <v>-25.93190544744522</v>
+        <v>-33.95610553025566</v>
       </c>
       <c r="F18">
-        <v>-4.122827786085593</v>
+        <v>-4.966324491129829</v>
       </c>
       <c r="G18">
-        <v>-4.754941019269079</v>
+        <v>-11.83318533132941</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.08913597482436637</v>
       </c>
       <c r="E19">
-        <v>-25.27927535888179</v>
+        <v>-34.13286772043406</v>
       </c>
       <c r="F19">
-        <v>-3.309991443721175</v>
+        <v>-4.665020758974759</v>
       </c>
       <c r="G19">
-        <v>-4.64937103256726</v>
+        <v>-11.64785768149547</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.1969193053520365</v>
       </c>
       <c r="E20">
-        <v>-27.45969936578301</v>
+        <v>-34.59636609206714</v>
       </c>
       <c r="F20">
-        <v>-3.305105732779464</v>
+        <v>-4.518974615656789</v>
       </c>
       <c r="G20">
-        <v>-4.124116566760955</v>
+        <v>-11.35132218590633</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.346940088760756</v>
       </c>
       <c r="E21">
-        <v>-28.52289902177786</v>
+        <v>-35.14449937866657</v>
       </c>
       <c r="F21">
-        <v>-3.179376956749957</v>
+        <v>-4.316520794045188</v>
       </c>
       <c r="G21">
-        <v>-4.301793545853639</v>
+        <v>-11.37101331077392</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.5058141231751024</v>
       </c>
       <c r="E22">
-        <v>-28.40490963150801</v>
+        <v>-36.08894886075829</v>
       </c>
       <c r="F22">
-        <v>-3.083932464599398</v>
+        <v>-4.307730159166679</v>
       </c>
       <c r="G22">
-        <v>-4.133955508103669</v>
+        <v>-11.4801288917483</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.6411524367169408</v>
       </c>
       <c r="E23">
-        <v>-27.61216402867325</v>
+        <v>-35.94502942832051</v>
       </c>
       <c r="F23">
-        <v>-3.211790144854099</v>
+        <v>-3.945728633938878</v>
       </c>
       <c r="G23">
-        <v>-4.6973408374313</v>
+        <v>-11.42273727427949</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.7261793111454496</v>
       </c>
       <c r="E24">
-        <v>-30.67689259013331</v>
+        <v>-36.13410001085176</v>
       </c>
       <c r="F24">
-        <v>-2.988758020222152</v>
+        <v>-4.148943725193653</v>
       </c>
       <c r="G24">
-        <v>-5.056389364438496</v>
+        <v>-11.17850839821084</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.7424984279694232</v>
       </c>
       <c r="E25">
-        <v>-30.70527932945039</v>
+        <v>-36.64058265776565</v>
       </c>
       <c r="F25">
-        <v>-2.713179237761021</v>
+        <v>-4.155317183990793</v>
       </c>
       <c r="G25">
-        <v>-3.784884965351836</v>
+        <v>-11.15560604417016</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-0.6770620365092365</v>
       </c>
       <c r="E26">
-        <v>-31.45816983254364</v>
+        <v>-37.16548260846872</v>
       </c>
       <c r="F26">
-        <v>-2.779937366752633</v>
+        <v>-3.932493807944351</v>
       </c>
       <c r="G26">
-        <v>-4.189122438970084</v>
+        <v>-11.5456379668794</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.5217752870906868</v>
       </c>
       <c r="E27">
-        <v>-28.52783052997222</v>
+        <v>-36.35981500505308</v>
       </c>
       <c r="F27">
-        <v>-2.984532518100472</v>
+        <v>-3.991669890098139</v>
       </c>
       <c r="G27">
-        <v>-5.732237236280708</v>
+        <v>-11.57334392249756</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.2756372516064151</v>
       </c>
       <c r="E28">
-        <v>-31.39671617602255</v>
+        <v>-37.43977907182433</v>
       </c>
       <c r="F28">
-        <v>-1.984828086808125</v>
+        <v>-4.057381791060015</v>
       </c>
       <c r="G28">
-        <v>-5.320153769734389</v>
+        <v>-11.17573747159447</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.05303845468245583</v>
       </c>
       <c r="E29">
-        <v>-29.91950304811344</v>
+        <v>-36.64390202921327</v>
       </c>
       <c r="F29">
-        <v>-2.38256372505789</v>
+        <v>-3.939153053495456</v>
       </c>
       <c r="G29">
-        <v>-4.195521723497495</v>
+        <v>-11.91510809124422</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.4553269340581214</v>
       </c>
       <c r="E30">
-        <v>-30.24957672582152</v>
+        <v>-36.34506123673609</v>
       </c>
       <c r="F30">
-        <v>-2.331473337122828</v>
+        <v>-3.784675786751793</v>
       </c>
       <c r="G30">
-        <v>-5.363965529401103</v>
+        <v>-11.91281057263996</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.9175885372214351</v>
       </c>
       <c r="E31">
-        <v>-29.65711873563501</v>
+        <v>-36.26543934249622</v>
       </c>
       <c r="F31">
-        <v>-1.884512794329105</v>
+        <v>-3.720476484667428</v>
       </c>
       <c r="G31">
-        <v>-6.397603920945588</v>
+        <v>-11.82775934719055</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>1.421146416063985</v>
       </c>
       <c r="E32">
-        <v>-30.01071330733893</v>
+        <v>-36.05801711904889</v>
       </c>
       <c r="F32">
-        <v>-1.726825603899593</v>
+        <v>-3.805921753898794</v>
       </c>
       <c r="G32">
-        <v>-6.055303443821566</v>
+        <v>-12.31474059601734</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>1.943677895963292</v>
       </c>
       <c r="E33">
-        <v>-29.21805148127332</v>
+        <v>-35.17555338917417</v>
       </c>
       <c r="F33">
-        <v>-2.724409414640774</v>
+        <v>-3.890998399635915</v>
       </c>
       <c r="G33">
-        <v>-4.285681120714006</v>
+        <v>-12.34377076985121</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>2.46782375703084</v>
       </c>
       <c r="E34">
-        <v>-28.55522779771862</v>
+        <v>-35.44276052647076</v>
       </c>
       <c r="F34">
-        <v>-2.818221194640415</v>
+        <v>-4.01799043595469</v>
       </c>
       <c r="G34">
-        <v>-4.905961485679552</v>
+        <v>-11.9918366052079</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>2.975465425750635</v>
       </c>
       <c r="E35">
-        <v>-28.60351491606241</v>
+        <v>-34.8528701810466</v>
       </c>
       <c r="F35">
-        <v>-2.473295635053923</v>
+        <v>-3.788958446224266</v>
       </c>
       <c r="G35">
-        <v>-6.030656432281692</v>
+        <v>-12.12347713803148</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>3.447517086158123</v>
       </c>
       <c r="E36">
-        <v>-29.36226526452159</v>
+        <v>-34.13968986652662</v>
       </c>
       <c r="F36">
-        <v>-2.813526008201348</v>
+        <v>-3.761714270713593</v>
       </c>
       <c r="G36">
-        <v>-5.112155504047519</v>
+        <v>-12.14186059741106</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>3.871807439590166</v>
       </c>
       <c r="E37">
-        <v>-27.33378514599973</v>
+        <v>-34.32759436700089</v>
       </c>
       <c r="F37">
-        <v>-2.638209502705457</v>
+        <v>-3.744389794851444</v>
       </c>
       <c r="G37">
-        <v>-5.498956334310425</v>
+        <v>-12.40659168200442</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>4.241349743002378</v>
       </c>
       <c r="E38">
-        <v>-27.1647960814555</v>
+        <v>-34.11462249865716</v>
       </c>
       <c r="F38">
-        <v>-2.696072622525808</v>
+        <v>-3.506030388165498</v>
       </c>
       <c r="G38">
-        <v>-4.953140070159706</v>
+        <v>-12.68682605135818</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>4.551032658981437</v>
       </c>
       <c r="E39">
-        <v>-26.12049374749465</v>
+        <v>-33.75092263720512</v>
       </c>
       <c r="F39">
-        <v>-3.348694425514774</v>
+        <v>-3.806562910268561</v>
       </c>
       <c r="G39">
-        <v>-6.404705041127325</v>
+        <v>-12.28122463297776</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>4.796129361219797</v>
       </c>
       <c r="E40">
-        <v>-25.25400647391899</v>
+        <v>-32.9360010971548</v>
       </c>
       <c r="F40">
-        <v>-2.571217774106255</v>
+        <v>-3.749706256842611</v>
       </c>
       <c r="G40">
-        <v>-6.429203078117932</v>
+        <v>-12.48549853493295</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>4.98052247119162</v>
       </c>
       <c r="E41">
-        <v>-26.34419130652555</v>
+        <v>-32.47264763668997</v>
       </c>
       <c r="F41">
-        <v>-2.409994283234194</v>
+        <v>-3.662272077477124</v>
       </c>
       <c r="G41">
-        <v>-6.07054519548437</v>
+        <v>-12.08545221196741</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>5.107589234973381</v>
       </c>
       <c r="E42">
-        <v>-25.28415252538805</v>
+        <v>-32.36824819691714</v>
       </c>
       <c r="F42">
-        <v>-2.570841695305385</v>
+        <v>-3.471314338681573</v>
       </c>
       <c r="G42">
-        <v>-5.864904038221462</v>
+        <v>-12.20352281862552</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>5.18126743936926</v>
       </c>
       <c r="E43">
-        <v>-24.8846052636913</v>
+        <v>-31.76361540436101</v>
       </c>
       <c r="F43">
-        <v>-2.693123634571842</v>
+        <v>-3.501621816847799</v>
       </c>
       <c r="G43">
-        <v>-5.552802357506671</v>
+        <v>-12.56837473196306</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>5.205934611733084</v>
       </c>
       <c r="E44">
-        <v>-24.17746593349754</v>
+        <v>-32.07323849345045</v>
       </c>
       <c r="F44">
-        <v>-2.679529297124499</v>
+        <v>-3.771542849947809</v>
       </c>
       <c r="G44">
-        <v>-5.981690153210332</v>
+        <v>-12.39361765403601</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>5.18740248555815</v>
       </c>
       <c r="E45">
-        <v>-23.68923756530858</v>
+        <v>-31.12783803181712</v>
       </c>
       <c r="F45">
-        <v>-2.660996233221666</v>
+        <v>-3.462787124637155</v>
       </c>
       <c r="G45">
-        <v>-5.924778564844721</v>
+        <v>-12.51665407900303</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>5.1314568681609</v>
       </c>
       <c r="E46">
-        <v>-21.4672149961729</v>
+        <v>-30.91874480146096</v>
       </c>
       <c r="F46">
-        <v>-2.745814428329113</v>
+        <v>-3.574308571341247</v>
       </c>
       <c r="G46">
-        <v>-5.664467058546288</v>
+        <v>-13.10924835162365</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>5.041175963831474</v>
       </c>
       <c r="E47">
-        <v>-21.8190864835169</v>
+        <v>-30.1275298228408</v>
       </c>
       <c r="F47">
-        <v>-2.693640535831189</v>
+        <v>-3.553814761795987</v>
       </c>
       <c r="G47">
-        <v>-5.852390176083017</v>
+        <v>-12.52679427998982</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>4.920416452847833</v>
       </c>
       <c r="E48">
-        <v>-21.30992750846449</v>
+        <v>-29.81723878383522</v>
       </c>
       <c r="F48">
-        <v>-2.329454605762206</v>
+        <v>-3.293786092220208</v>
       </c>
       <c r="G48">
-        <v>-6.060454652680672</v>
+        <v>-12.84525882923108</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>4.769537981890265</v>
       </c>
       <c r="E49">
-        <v>-21.05982894596887</v>
+        <v>-29.46878855860401</v>
       </c>
       <c r="F49">
-        <v>-2.680053653690472</v>
+        <v>-3.409572802681315</v>
       </c>
       <c r="G49">
-        <v>-5.023379914866423</v>
+        <v>-12.69555595994524</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>4.592547909621512</v>
       </c>
       <c r="E50">
-        <v>-19.95554697377643</v>
+        <v>-28.74493463084795</v>
       </c>
       <c r="F50">
-        <v>-2.29633896210049</v>
+        <v>-3.458815931308134</v>
       </c>
       <c r="G50">
-        <v>-6.020996260398099</v>
+        <v>-12.75395398325798</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>4.389423614872964</v>
       </c>
       <c r="E51">
-        <v>-21.88234020845604</v>
+        <v>-28.24380011173712</v>
       </c>
       <c r="F51">
-        <v>-2.718628238536636</v>
+        <v>-3.528734281941427</v>
       </c>
       <c r="G51">
-        <v>-6.879513414006217</v>
+        <v>-13.43477760504572</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>4.159686574634604</v>
       </c>
       <c r="E52">
-        <v>-19.76646959853417</v>
+        <v>-27.40401724938469</v>
       </c>
       <c r="F52">
-        <v>-2.063127858822942</v>
+        <v>-3.411049781760506</v>
       </c>
       <c r="G52">
-        <v>-5.822452912771388</v>
+        <v>-13.09027892568362</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>3.903101478821057</v>
       </c>
       <c r="E53">
-        <v>-17.85072131195926</v>
+        <v>-27.38080429162137</v>
       </c>
       <c r="F53">
-        <v>-2.544086256562363</v>
+        <v>-3.493406068946833</v>
       </c>
       <c r="G53">
-        <v>-5.369321992083644</v>
+        <v>-13.2217671734124</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>3.621779000024826</v>
       </c>
       <c r="E54">
-        <v>-18.60682703159796</v>
+        <v>-27.05033437243762</v>
       </c>
       <c r="F54">
-        <v>-2.794143039343242</v>
+        <v>-3.338295929507431</v>
       </c>
       <c r="G54">
-        <v>-6.80387075897941</v>
+        <v>-12.88010563157745</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>3.315663087178746</v>
       </c>
       <c r="E55">
-        <v>-18.16877868388799</v>
+        <v>-26.35433055982873</v>
       </c>
       <c r="F55">
-        <v>-2.793687437271702</v>
+        <v>-3.80662172435416</v>
       </c>
       <c r="G55">
-        <v>-5.798716301254813</v>
+        <v>-13.04891034862489</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>2.983961562437769</v>
       </c>
       <c r="E56">
-        <v>-16.52244290145142</v>
+        <v>-27.29428779570483</v>
       </c>
       <c r="F56">
-        <v>-2.252592051191245</v>
+        <v>-3.462695175855445</v>
       </c>
       <c r="G56">
-        <v>-6.488024851259703</v>
+        <v>-13.29488388219274</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>2.632547560830694</v>
       </c>
       <c r="E57">
-        <v>-17.95027075606988</v>
+        <v>-26.80610018378194</v>
       </c>
       <c r="F57">
-        <v>-2.64049165490017</v>
+        <v>-3.5326913930246</v>
       </c>
       <c r="G57">
-        <v>-6.21335550895745</v>
+        <v>-12.70460368090407</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>2.267210522544187</v>
       </c>
       <c r="E58">
-        <v>-17.12729758923392</v>
+        <v>-25.64724104284905</v>
       </c>
       <c r="F58">
-        <v>-3.05746198424294</v>
+        <v>-3.567390875160468</v>
       </c>
       <c r="G58">
-        <v>-5.626889056130021</v>
+        <v>-13.24029298625016</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>1.89398321130777</v>
       </c>
       <c r="E59">
-        <v>-17.10638056779249</v>
+        <v>-26.39612837491952</v>
       </c>
       <c r="F59">
-        <v>-3.278549930580517</v>
+        <v>-3.567333717809675</v>
       </c>
       <c r="G59">
-        <v>-6.201454097743771</v>
+        <v>-13.37298627255523</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>1.520182652484372</v>
       </c>
       <c r="E60">
-        <v>-15.64921273007833</v>
+        <v>-25.59936601563997</v>
       </c>
       <c r="F60">
-        <v>-3.308891371810257</v>
+        <v>-3.704877498105311</v>
       </c>
       <c r="G60">
-        <v>-6.243670174460557</v>
+        <v>-13.5614738381064</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>1.159340506898267</v>
       </c>
       <c r="E61">
-        <v>-15.94547908508215</v>
+        <v>-26.17251232842076</v>
       </c>
       <c r="F61">
-        <v>-2.831765001676187</v>
+        <v>-3.505506859966928</v>
       </c>
       <c r="G61">
-        <v>-6.244054197743113</v>
+        <v>-13.92349026918955</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>0.8217940901467597</v>
       </c>
       <c r="E62">
-        <v>-16.0008260944039</v>
+        <v>-25.6047594281831</v>
       </c>
       <c r="F62">
-        <v>-2.793878790141749</v>
+        <v>-3.676306278015353</v>
       </c>
       <c r="G62">
-        <v>-6.829136842535127</v>
+        <v>-14.29429619867947</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>0.516951184547999</v>
       </c>
       <c r="E63">
-        <v>-16.61151345670828</v>
+        <v>-25.76666143090533</v>
       </c>
       <c r="F63">
-        <v>-2.75160140300507</v>
+        <v>-3.582726440888496</v>
       </c>
       <c r="G63">
-        <v>-6.387533241415126</v>
+        <v>-13.57242346747754</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>0.2566760164915351</v>
       </c>
       <c r="E64">
-        <v>-16.58055227991784</v>
+        <v>-25.5352111243733</v>
       </c>
       <c r="F64">
-        <v>-2.940619105343264</v>
+        <v>-3.830815022720322</v>
       </c>
       <c r="G64">
-        <v>-6.82017850630586</v>
+        <v>-13.64077961177241</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>0.05072102014957902</v>
       </c>
       <c r="E65">
-        <v>-15.66131734110084</v>
+        <v>-24.50621050408437</v>
       </c>
       <c r="F65">
-        <v>-3.059426871722381</v>
+        <v>-3.686417330533924</v>
       </c>
       <c r="G65">
-        <v>-6.728588953416383</v>
+        <v>-14.04767876400423</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.09336635259832872</v>
       </c>
       <c r="E66">
-        <v>-16.3186344002622</v>
+        <v>-24.8315904184835</v>
       </c>
       <c r="F66">
-        <v>-3.022034367160011</v>
+        <v>-3.589719518502929</v>
       </c>
       <c r="G66">
-        <v>-7.16639535880284</v>
+        <v>-13.61898132466908</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-0.1706353189586124</v>
       </c>
       <c r="E67">
-        <v>-13.28926189961703</v>
+        <v>-24.5927224715269</v>
       </c>
       <c r="F67">
-        <v>-2.879966044110284</v>
+        <v>-3.711320539764285</v>
       </c>
       <c r="G67">
-        <v>-7.151196644232046</v>
+        <v>-13.43246022316823</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-0.1753906187919881</v>
       </c>
       <c r="E68">
-        <v>-15.64741492589729</v>
+        <v>-24.40594556108054</v>
       </c>
       <c r="F68">
-        <v>-3.012313475688159</v>
+        <v>-3.808595723875031</v>
       </c>
       <c r="G68">
-        <v>-7.877894495557465</v>
+        <v>-13.84556995883173</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.1083761476083782</v>
       </c>
       <c r="E69">
-        <v>-15.21567021400599</v>
+        <v>-24.6610888436207</v>
       </c>
       <c r="F69">
-        <v>-3.071872263582041</v>
+        <v>-3.588896121304546</v>
       </c>
       <c r="G69">
-        <v>-6.174320866503904</v>
+        <v>-13.71964673815447</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>0.02883408451368083</v>
       </c>
       <c r="E70">
-        <v>-15.23256142205461</v>
+        <v>-24.93735292893264</v>
       </c>
       <c r="F70">
-        <v>-2.400841651800662</v>
+        <v>-3.801011191934999</v>
       </c>
       <c r="G70">
-        <v>-7.659828860885671</v>
+        <v>-13.6727958976827</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>0.2316829856616194</v>
       </c>
       <c r="E71">
-        <v>-14.35241627087181</v>
+        <v>-24.47672560982043</v>
       </c>
       <c r="F71">
-        <v>-3.433375111633356</v>
+        <v>-3.770029422702895</v>
       </c>
       <c r="G71">
-        <v>-6.784610005031929</v>
+        <v>-13.48196281061695</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>0.4914464325352266</v>
       </c>
       <c r="E72">
-        <v>-16.65039946301215</v>
+        <v>-24.94002925707117</v>
       </c>
       <c r="F72">
-        <v>-3.452046512892457</v>
+        <v>-3.762303239936983</v>
       </c>
       <c r="G72">
-        <v>-5.99046640943494</v>
+        <v>-13.56600100913135</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>0.7969284556540046</v>
       </c>
       <c r="E73">
-        <v>-15.09495015390952</v>
+        <v>-24.7342916259547</v>
       </c>
       <c r="F73">
-        <v>-3.402187078917954</v>
+        <v>-4.090428680227299</v>
       </c>
       <c r="G73">
-        <v>-7.103448645919138</v>
+        <v>-13.52700774849705</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>1.137042122041124</v>
       </c>
       <c r="E74">
-        <v>-15.08387350648676</v>
+        <v>-25.07356942708337</v>
       </c>
       <c r="F74">
-        <v>-3.230248655690681</v>
+        <v>-4.117807051257225</v>
       </c>
       <c r="G74">
-        <v>-5.846209387561197</v>
+        <v>-13.45113501055526</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>1.500133361782181</v>
       </c>
       <c r="E75">
-        <v>-15.73348310288707</v>
+        <v>-25.55021395876071</v>
       </c>
       <c r="F75">
-        <v>-3.284546482209383</v>
+        <v>-3.811825528378546</v>
       </c>
       <c r="G75">
-        <v>-6.24302130753486</v>
+        <v>-13.17405559110042</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>1.870781624519041</v>
       </c>
       <c r="E76">
-        <v>-17.713599119007</v>
+        <v>-26.06496107073859</v>
       </c>
       <c r="F76">
-        <v>-3.235105373773294</v>
+        <v>-4.008125408554751</v>
       </c>
       <c r="G76">
-        <v>-6.907835131094682</v>
+        <v>-12.98410310914812</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>2.2417290418935</v>
       </c>
       <c r="E77">
-        <v>-17.94947827311854</v>
+        <v>-25.4558088611228</v>
       </c>
       <c r="F77">
-        <v>-3.482555284337562</v>
+        <v>-4.106207422515824</v>
       </c>
       <c r="G77">
-        <v>-6.263361299328142</v>
+        <v>-13.14238691247175</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>2.606645891610286</v>
       </c>
       <c r="E78">
-        <v>-18.92238015740044</v>
+        <v>-26.17055602764945</v>
       </c>
       <c r="F78">
-        <v>-3.238028682337774</v>
+        <v>-3.968643761402521</v>
       </c>
       <c r="G78">
-        <v>-6.360178203624128</v>
+        <v>-12.9217787788258</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>2.959514985325222</v>
       </c>
       <c r="E79">
-        <v>-17.74930160808347</v>
+        <v>-26.64958253665483</v>
       </c>
       <c r="F79">
-        <v>-3.204192359035622</v>
+        <v>-4.233230936795906</v>
       </c>
       <c r="G79">
-        <v>-5.470396257943133</v>
+        <v>-12.97331735178117</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>3.29612566069067</v>
       </c>
       <c r="E80">
-        <v>-18.92089481792593</v>
+        <v>-26.87892257429928</v>
       </c>
       <c r="F80">
-        <v>-3.565356404819193</v>
+        <v>-4.180413402826006</v>
       </c>
       <c r="G80">
-        <v>-5.93141289810542</v>
+        <v>-12.99775910949761</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>3.617873448758183</v>
       </c>
       <c r="E81">
-        <v>-19.27821858797516</v>
+        <v>-27.30482102624667</v>
       </c>
       <c r="F81">
-        <v>-3.311580252399744</v>
+        <v>-4.38005988730952</v>
       </c>
       <c r="G81">
-        <v>-4.981180390877332</v>
+        <v>-12.98689058849218</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>3.925358210423514</v>
       </c>
       <c r="E82">
-        <v>-19.75761190337516</v>
+        <v>-27.61633928170832</v>
       </c>
       <c r="F82">
-        <v>-3.386874707477205</v>
+        <v>-4.351294829247307</v>
       </c>
       <c r="G82">
-        <v>-5.215974212159063</v>
+        <v>-12.62391906502095</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>4.214992913179835</v>
       </c>
       <c r="E83">
-        <v>-21.05079916879757</v>
+        <v>-28.24610510500703</v>
       </c>
       <c r="F83">
-        <v>-3.419136304346635</v>
+        <v>-4.424965684215282</v>
       </c>
       <c r="G83">
-        <v>-5.649705335986678</v>
+        <v>-12.61502362915693</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>4.487072155899608</v>
       </c>
       <c r="E84">
-        <v>-23.30918538421484</v>
+        <v>-29.20451587246439</v>
       </c>
       <c r="F84">
-        <v>-3.918007318804193</v>
+        <v>-4.48988235247047</v>
       </c>
       <c r="G84">
-        <v>-5.239641302219313</v>
+        <v>-12.84086904584601</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>4.739563306859755</v>
       </c>
       <c r="E85">
-        <v>-21.99400332053718</v>
+        <v>-29.32388644730658</v>
       </c>
       <c r="F85">
-        <v>-3.7879031061531</v>
+        <v>-4.347056073247183</v>
       </c>
       <c r="G85">
-        <v>-4.747277106345666</v>
+        <v>-12.45418739522252</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>4.968368959558992</v>
       </c>
       <c r="E86">
-        <v>-22.84982150935077</v>
+        <v>-31.16279332268233</v>
       </c>
       <c r="F86">
-        <v>-3.653570906278118</v>
+        <v>-4.626010452874722</v>
       </c>
       <c r="G86">
-        <v>-4.53240945866481</v>
+        <v>-12.05283340676898</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>5.164522689913913</v>
       </c>
       <c r="E87">
-        <v>-24.82132436790811</v>
+        <v>-31.16333673956325</v>
       </c>
       <c r="F87">
-        <v>-4.130273980669357</v>
+        <v>-4.643611603449406</v>
       </c>
       <c r="G87">
-        <v>-4.302187500772813</v>
+        <v>-12.43354283323962</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>5.320880691269245</v>
       </c>
       <c r="E88">
-        <v>-25.27112863414199</v>
+        <v>-31.99495476327985</v>
       </c>
       <c r="F88">
-        <v>-3.990266635717796</v>
+        <v>-4.652061779325363</v>
       </c>
       <c r="G88">
-        <v>-4.911989989106565</v>
+        <v>-12.45996429718855</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>5.427388351131826</v>
       </c>
       <c r="E89">
-        <v>-28.37189705599209</v>
+        <v>-33.25561399990517</v>
       </c>
       <c r="F89">
-        <v>-4.121250574550663</v>
+        <v>-4.788893992021994</v>
       </c>
       <c r="G89">
-        <v>-4.223916272587823</v>
+        <v>-12.31158564611841</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>5.473930480776033</v>
       </c>
       <c r="E90">
-        <v>-28.33324200186262</v>
+        <v>-34.59667855677367</v>
       </c>
       <c r="F90">
-        <v>-4.252623846062844</v>
+        <v>-5.017218555990428</v>
       </c>
       <c r="G90">
-        <v>-3.987510215628468</v>
+        <v>-12.42305171442567</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>5.450881255206035</v>
       </c>
       <c r="E91">
-        <v>-28.37155289196751</v>
+        <v>-34.47457731210485</v>
       </c>
       <c r="F91">
-        <v>-3.082330402042384</v>
+        <v>-5.21869904590374</v>
       </c>
       <c r="G91">
-        <v>-3.83651623358231</v>
+        <v>-11.9944916627304</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>5.350096049505962</v>
       </c>
       <c r="E92">
-        <v>-31.86635289417303</v>
+        <v>-36.38790286508566</v>
       </c>
       <c r="F92">
-        <v>-4.249606931981849</v>
+        <v>-4.867921898983872</v>
       </c>
       <c r="G92">
-        <v>-4.567431719924759</v>
+        <v>-12.56530916679369</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>5.168949872334287</v>
       </c>
       <c r="E93">
-        <v>-34.59042473416908</v>
+        <v>-37.33912241581884</v>
       </c>
       <c r="F93">
-        <v>-4.210898979983833</v>
+        <v>-5.235420470296651</v>
       </c>
       <c r="G93">
-        <v>-4.867463151603368</v>
+        <v>-12.78546375570077</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>4.906821710879513</v>
       </c>
       <c r="E94">
-        <v>-35.58380211367666</v>
+        <v>-39.12718811351047</v>
       </c>
       <c r="F94">
-        <v>-3.937478922974398</v>
+        <v>-5.118247072803258</v>
       </c>
       <c r="G94">
-        <v>-5.335908655955779</v>
+        <v>-12.31789223537072</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>4.569567551951343</v>
       </c>
       <c r="E95">
-        <v>-36.23285244353703</v>
+        <v>-40.61647868159804</v>
       </c>
       <c r="F95">
-        <v>-4.154123506563358</v>
+        <v>-5.347955010334366</v>
       </c>
       <c r="G95">
-        <v>-5.862119869422935</v>
+        <v>-13.30585503010989</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>4.161370763505277</v>
       </c>
       <c r="E96">
-        <v>-38.42853514360709</v>
+        <v>-42.57648827312392</v>
       </c>
       <c r="F96">
-        <v>-4.02372191001466</v>
+        <v>-5.47788775093308</v>
       </c>
       <c r="G96">
-        <v>-5.876504189791068</v>
+        <v>-12.96657045997214</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>3.704648494503708</v>
       </c>
       <c r="E97">
-        <v>-40.60940973367207</v>
+        <v>-43.93813021588328</v>
       </c>
       <c r="F97">
-        <v>-4.44845652702387</v>
+        <v>-5.41965517925108</v>
       </c>
       <c r="G97">
-        <v>-6.264066445528007</v>
+        <v>-13.28579974523298</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>3.20618383841342</v>
       </c>
       <c r="E98">
-        <v>-42.89992094369975</v>
+        <v>-45.37583920078648</v>
       </c>
       <c r="F98">
-        <v>-4.870836095506921</v>
+        <v>-5.76884683096199</v>
       </c>
       <c r="G98">
-        <v>-7.563511848966115</v>
+        <v>-13.35263634912533</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>2.698941381223779</v>
       </c>
       <c r="E99">
-        <v>-45.81441511571834</v>
+        <v>-46.84812534897524</v>
       </c>
       <c r="F99">
-        <v>-4.614304793105762</v>
+        <v>-5.750795048520183</v>
       </c>
       <c r="G99">
-        <v>-6.434470156070913</v>
+        <v>-13.7610533864869</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>2.180836357451361</v>
       </c>
       <c r="E100">
-        <v>-47.34054708409531</v>
+        <v>-48.67557065663758</v>
       </c>
       <c r="F100">
-        <v>-5.205388838475558</v>
+        <v>-5.839959687390119</v>
       </c>
       <c r="G100">
-        <v>-7.239369714124995</v>
+        <v>-13.89128693745629</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>1.709618940050952</v>
       </c>
       <c r="E101">
-        <v>-49.14390091003684</v>
+        <v>-50.01666351646863</v>
       </c>
       <c r="F101">
-        <v>-5.403453141219725</v>
+        <v>-6.289080198186642</v>
       </c>
       <c r="G101">
-        <v>-7.757870667031187</v>
+        <v>-14.23156301598305</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>1.239983874302326</v>
       </c>
       <c r="E102">
-        <v>-51.15027867904576</v>
+        <v>-53.00003691026239</v>
       </c>
       <c r="F102">
-        <v>-5.227519502008749</v>
+        <v>-6.13805349585934</v>
       </c>
       <c r="G102">
-        <v>-8.350219959281903</v>
+        <v>-14.58394907009246</v>
       </c>
     </row>
   </sheetData>
